--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484751_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484751_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.31</v>
+        <v>3.9093</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3574</v>
+        <v>1.2213</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9526</v>
+        <v>2.688</v>
       </c>
       <c r="G2" t="n">
         <v>2.3425</v>
@@ -610,13 +610,13 @@
         <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5902</v>
+        <v>1.1895</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7824</v>
+        <v>0.6463</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8078</v>
+        <v>0.5432</v>
       </c>
       <c r="V2" t="n">
         <v>0.9434</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1261</v>
+        <v>3.5252</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5737</v>
+        <v>3.9489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5525</v>
+        <v>-0.4237</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7463</v>
+        <v>2.9041</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4751</v>
+        <v>-2.4839</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2214</v>
+        <v>5.388</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4152</v>
+        <v>4.2926</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1684</v>
+        <v>-0.792</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2468</v>
+        <v>5.0846</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6688</v>
+        <v>-1.3885</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6434</v>
+        <v>-1.6919</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9746</v>
+        <v>0.3035</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>1.512</v>
+        <v>-0.5111</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2533</v>
+        <v>-0.3437</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2587</v>
+        <v>-0.1675</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.485</v>
+        <v>2.7411</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3055</v>
+        <v>2.6912</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8205</v>
+        <v>0.0499</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9041</v>
+        <v>0.7463</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.4839</v>
+        <v>-0.4751</v>
       </c>
       <c r="I5" t="n">
-        <v>5.388</v>
+        <v>1.2214</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2926</v>
+        <v>1.4152</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.792</v>
+        <v>1.1684</v>
       </c>
       <c r="L5" t="n">
-        <v>5.0846</v>
+        <v>0.2468</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3885</v>
+        <v>-0.6688</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6919</v>
+        <v>-1.6434</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3035</v>
+        <v>0.9746</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1322</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5513</v>
+        <v>1.1269</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9871</v>
+        <v>0.3709</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5643</v>
+        <v>0.7561</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.775</v>
+        <v>1.0311</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6479</v>
+        <v>1.7453</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8729</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1207</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8965</v>
+        <v>-0.6403</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.485</v>
+        <v>-0.3262</v>
       </c>
       <c r="V6" t="n">
         <v>3.113</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3688</v>
+        <v>0.3113</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3307</v>
+        <v>-1.0116</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9618</v>
+        <v>1.3229</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0639</v>
+        <v>0.5619</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2496</v>
+        <v>-0.5165</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8142</v>
+        <v>1.0784</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4695</v>
+        <v>-0.7254</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2154</v>
+        <v>-0.8077</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6849</v>
+        <v>0.0823</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5944</v>
+        <v>1.2873</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.465</v>
+        <v>0.2911</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1294</v>
+        <v>0.9962</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3774</v>
+        <v>-3.0192</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8101</v>
+        <v>1.2026</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2533</v>
+        <v>0.9974</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5568</v>
+        <v>0.2052</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2452</v>
+        <v>1.566</v>
       </c>
       <c r="W8" t="n">
         <v>2.4904</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4005</v>
+        <v>0.1606</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1678</v>
+        <v>1.5457</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7674</v>
+        <v>-1.3851</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5619</v>
+        <v>-2.0639</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5165</v>
+        <v>-0.2496</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0784</v>
+        <v>-1.8142</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7254</v>
+        <v>-0.4695</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8077</v>
+        <v>1.2154</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0823</v>
+        <v>-1.6849</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2873</v>
+        <v>-1.5944</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2911</v>
+        <v>-1.465</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9962</v>
+        <v>-0.1294</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.0192</v>
+        <v>0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7548</v>
+        <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4908</v>
+        <v>0.6018</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.4683</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3503</v>
+        <v>0.1336</v>
       </c>
       <c r="V9" t="n">
-        <v>1.566</v>
+        <v>1.2452</v>
       </c>
       <c r="W9" t="n">
         <v>2.4904</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9244</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1119</v>
+        <v>-2.0237</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1648</v>
+        <v>1.3853</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2768</v>
+        <v>-3.409</v>
       </c>
       <c r="G10" t="n">
         <v>0.0282</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9729</v>
+        <v>0.0611</v>
       </c>
       <c r="T10" t="n">
-        <v>1.064</v>
+        <v>0.2845</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0911</v>
+        <v>-0.2234</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4904</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8178</v>
+        <v>-3.4654</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6604</v>
+        <v>-2.6843</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1574</v>
+        <v>-0.7811</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3463</v>
+        <v>-0.5003</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.409</v>
+        <v>-2.4229</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06270000000000001</v>
+        <v>1.9226</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3083</v>
+        <v>1.9603</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4572</v>
+        <v>-0.1785</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1489</v>
+        <v>2.1388</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.038</v>
+        <v>-2.4606</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9518</v>
+        <v>-2.2445</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0863</v>
+        <v>-0.2162</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9435</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>0.472</v>
+        <v>-0.7005</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5349</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.1698</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8753</v>
+        <v>-3.7422</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0942</v>
+        <v>-2.7965</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7811</v>
+        <v>-0.9457</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5003</v>
+        <v>-3.3463</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4229</v>
+        <v>-3.409</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9226</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9603</v>
+        <v>-1.3083</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1785</v>
+        <v>-1.4572</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1388</v>
+        <v>0.1489</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4606</v>
+        <v>-2.038</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2445</v>
+        <v>-1.9518</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2162</v>
+        <v>-0.0863</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2079</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7175</v>
+        <v>-1.887</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1104</v>
+        <v>0.5476</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9406</v>
+        <v>0.3988</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1698</v>
+        <v>0.1488</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.278099999999999</v>
+        <v>5.866</v>
       </c>
       <c r="E13" t="n">
-        <v>8.876299999999997</v>
+        <v>9.464</v>
       </c>
       <c r="F13" t="n">
         <v>-3.598</v>
@@ -1435,7 +1435,7 @@
         <v>3.970499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.6945</v>
+        <v>-8.694500000000001</v>
       </c>
       <c r="I13" t="n">
         <v>12.6652</v>
@@ -1468,10 +1468,10 @@
         <v>9.435</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2898</v>
+        <v>2.8776</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3899</v>
+        <v>1.9777</v>
       </c>
       <c r="U13" t="n">
         <v>0.9000000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7656</v>
+        <v>2.5076</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4406</v>
+        <v>2.6612</v>
       </c>
       <c r="F14" t="n">
-        <v>0.325</v>
+        <v>-0.1536</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2994</v>
@@ -1546,13 +1546,13 @@
         <v>2.6418</v>
       </c>
       <c r="S14" t="n">
-        <v>1.763</v>
+        <v>0.505</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1873</v>
+        <v>0.4079</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5756</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3398</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>F. LOPEZ ZOROA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4718</v>
+        <v>2.0842</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8132</v>
+        <v>3.498</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6586</v>
+        <v>-1.4138</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8107</v>
+        <v>2.1714</v>
       </c>
       <c r="H15" t="n">
-        <v>2.995</v>
+        <v>3.3707</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1843</v>
+        <v>-1.1993</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1525</v>
+        <v>3.5858</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7524</v>
+        <v>3.4865</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5999</v>
+        <v>0.0993</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3417</v>
+        <v>-1.4144</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2426</v>
+        <v>-0.1158</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5843</v>
+        <v>-1.2986</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1322</v>
+        <v>2.0757</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2069</v>
+        <v>-0.9366</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9994</v>
+        <v>-0.7104</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7925</v>
+        <v>-0.2262</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2642</v>
+        <v>-1.2262</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6036</v>
+        <v>0.6226</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8678</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. LOPEZ ZOROA</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2097</v>
+        <v>1.8713</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6211</v>
+        <v>1.3978</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4114</v>
+        <v>0.4735</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1714</v>
+        <v>1.8107</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3707</v>
+        <v>2.995</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1993</v>
+        <v>-1.1843</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5858</v>
+        <v>2.1525</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4865</v>
+        <v>2.7524</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0993</v>
+        <v>-0.5999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4144</v>
+        <v>-0.3417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1158</v>
+        <v>0.2426</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2986</v>
+        <v>-0.5843</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8112</v>
+        <v>0.1925</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5873</v>
+        <v>-0.4148</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2239</v>
+        <v>0.6073</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2262</v>
+        <v>-1.2642</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6226</v>
+        <v>0.6036</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8488</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6536</v>
+        <v>0.502</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2228</v>
+        <v>1.8331</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5692</v>
+        <v>-1.3311</v>
       </c>
       <c r="G17" t="n">
         <v>1.8127</v>
@@ -1780,13 +1780,13 @@
         <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2158</v>
+        <v>-0.3674</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4173</v>
+        <v>0.0276</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6331</v>
+        <v>-0.395</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8868</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.541</v>
+        <v>0.2125</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0365</v>
+        <v>1.5493</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4955</v>
+        <v>-1.3368</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7396</v>
@@ -1858,13 +1858,13 @@
         <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7336</v>
+        <v>0.4052</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.4004</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.154</v>
+        <v>0.0047</v>
       </c>
       <c r="V18" t="n">
         <v>2.4904</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4165</v>
+        <v>-0.6294</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1483</v>
+        <v>-0.4406</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2682</v>
+        <v>-0.1888</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8883</v>
@@ -1936,13 +1936,13 @@
         <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0188</v>
+        <v>-0.1941</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3556</v>
+        <v>0.0633</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3368</v>
+        <v>-0.2575</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3018</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2279</v>
+        <v>-1.4869</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5732</v>
+        <v>-1.9886</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3453</v>
+        <v>0.5017</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7551</v>
@@ -2014,13 +2014,13 @@
         <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8694</v>
+        <v>-1.1284</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5285</v>
+        <v>-0.9439</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3409</v>
+        <v>-0.1845</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2452</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8757</v>
+        <v>-2.5221</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1022</v>
+        <v>-1.9073</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7736</v>
+        <v>-0.6148</v>
       </c>
       <c r="G21" t="n">
         <v>-1.173</v>
@@ -2092,13 +2092,13 @@
         <v>2.2644</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1087</v>
+        <v>0.4623</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.053</v>
+        <v>0.1419</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1617</v>
+        <v>0.3204</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3018</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6494</v>
+        <v>-3.5556</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.173</v>
+        <v>-2.3679</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4763</v>
+        <v>-1.1877</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1085</v>
@@ -2170,13 +2170,13 @@
         <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1634</v>
+        <v>-0.0697</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4761</v>
+        <v>0.2812</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6395</v>
+        <v>-0.3509</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2452</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7503</v>
+        <v>-3.612</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5394</v>
+        <v>-0.6368</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2109</v>
+        <v>-2.9752</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8014</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6472</v>
+        <v>-0.5089</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0559</v>
+        <v>-0.1533</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5914</v>
+        <v>-0.3556</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2781</v>
+        <v>-4.628400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>3.5981</v>
+        <v>3.598199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.876200000000001</v>
+        <v>-8.226600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9705</v>
@@ -2326,13 +2326,13 @@
         <v>16.983</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2898</v>
+        <v>-1.6401</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9001999999999998</v>
+        <v>-0.9001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3898</v>
+        <v>-0.7402000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-6.565800000000001</v>
